--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -776,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -826,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -834,22 +834,22 @@
       <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>沪A66391D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>06:40</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -882,12 +882,12 @@
       <c r="M4" s="2" t="inlineStr"/>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -937,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A57022D</t>
+          <t>沪A66391D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -955,7 +955,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:00</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1012,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1048,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,32 +632,36 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>07:35</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -665,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -689,17 +693,17 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
@@ -709,13 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +751,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:07</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -776,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +812,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -854,32 +870,36 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:03</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="inlineStr"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -887,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -911,33 +931,37 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X4" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y4" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -998,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1037,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1048,7 +1072,7 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1172,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1183,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1244,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1259,7 +1283,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1270,7 +1294,7 @@
       <c r="AB7" s="2" t="inlineStr"/>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1331,7 +1355,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1381,7 +1405,7 @@
       <c r="AB8" s="2" t="inlineStr"/>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1466,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1481,7 +1505,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1492,7 +1516,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1577,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:10</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1627,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1688,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1727,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1738,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1799,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1849,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1833,22 +1857,22 @@
       <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -1881,12 +1905,12 @@
       <c r="M13" s="2" t="inlineStr"/>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:00</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1960,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1944,22 +1968,22 @@
       <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A35616D</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>07:30</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1992,12 +2016,12 @@
       <c r="M14" s="2" t="inlineStr"/>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>07:00</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2011,7 +2035,7 @@
       <c r="T14" s="2" t="inlineStr"/>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>07:30</t>
+          <t>07:42</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
@@ -2047,7 +2071,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2132,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2182,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2243,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2293,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2301,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>08:03</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2349,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2368,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>08:03</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2393,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2404,1129 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:03</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:14</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:23</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr"/>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr"/>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,17 +713,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,7 +827,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1133,7 +1133,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1211,32 +1211,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1244,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1268,17 +1272,17 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
@@ -1288,13 +1292,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1322,32 +1330,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:48</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1355,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1379,33 +1391,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1433,32 +1449,36 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr"/>
       <c r="K9" s="2" t="inlineStr"/>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1466,7 +1486,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1490,17 +1510,17 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X9" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y9" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z9" s="2" t="inlineStr">
@@ -1510,13 +1530,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1544,32 +1568,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:55</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>105分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1577,7 +1605,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:10</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1601,33 +1629,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1655,32 +1687,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:59</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1688,7 +1724,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1712,17 +1748,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1732,13 +1768,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1799,7 +1839,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1838,7 +1878,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1877,32 +1917,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -1910,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1934,33 +1978,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1988,32 +2036,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:21</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2021,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2045,33 +2097,37 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2099,32 +2155,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2132,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2156,17 +2216,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2176,13 +2236,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2274,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:12</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2243,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2267,33 +2335,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2321,32 +2393,36 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr"/>
       <c r="K17" s="2" t="inlineStr"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -2354,7 +2430,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2378,33 +2454,37 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X17" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y17" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2432,32 +2512,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2465,7 +2549,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2489,17 +2573,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2509,17 +2593,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2664,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2691,7 +2775,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2730,7 +2814,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2745,7 +2829,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2890,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2860,7 +2944,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2921,7 +3005,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3032,7 +3116,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3143,7 +3227,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3254,7 +3338,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3298,13 +3382,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB25" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3453,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3409,13 +3497,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>112.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3423,22 +3515,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A58633D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:10</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3471,12 +3563,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3490,43 +3582,963 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>108.0</t>
+        </is>
+      </c>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:05</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>09:10</t>
         </is>
       </c>
-      <c r="V27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W27" s="2" t="inlineStr">
+      <c r="W29" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X27" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y27" s="2" t="inlineStr">
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z27" s="2" t="inlineStr">
+      <c r="Z29" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>105.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AB27" s="2" t="inlineStr"/>
-      <c r="AC27" s="2" t="inlineStr">
+      <c r="AB30" s="2" t="inlineStr"/>
+      <c r="AC30" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC35"/>
+  <dimension ref="A1:AC39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -718,12 +718,12 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,18 +1061,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1133,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1172,18 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1302,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1421,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1486,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1525,7 +1533,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1540,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1605,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1659,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1724,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1778,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1839,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1954,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2254,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2373,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2430,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2484,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2522,24 +2530,24 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2549,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2598,12 +2606,12 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2631,32 +2639,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -2664,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2688,17 +2700,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2708,13 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2742,32 +2758,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:43</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -2775,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2799,17 +2819,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2819,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2857,32 +2877,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2890,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2914,37 +2938,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2972,32 +2996,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:51</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -3005,7 +3033,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3029,17 +3057,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3049,13 +3077,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3083,32 +3115,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3116,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3140,33 +3176,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB23" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3194,32 +3234,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:52</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -3227,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3251,33 +3295,37 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3338,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3377,7 +3425,7 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA25" s="2" t="inlineStr">
@@ -3392,7 +3440,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3507,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3616,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3622,7 +3670,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3731,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3737,7 +3785,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3798,7 +3846,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3852,7 +3900,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3913,7 +3961,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,7 +4072,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4078,7 +4126,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4139,7 +4187,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4193,7 +4241,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4254,7 +4302,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4308,7 +4356,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4369,7 +4417,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4423,7 +4471,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4431,22 +4479,22 @@
       <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>沪A55207D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>10:10</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -4479,12 +4527,12 @@
       <c r="M35" s="2" t="inlineStr"/>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>06:00</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4528,17 +4576,477 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB35" s="2" t="inlineStr">
-        <is>
-          <t>102.0</t>
-        </is>
-      </c>
-      <c r="AC35" s="2" t="inlineStr">
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
         <is>
           <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC39"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1962,7 +1962,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2081,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2319,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3353,32 +3353,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3410,17 +3414,17 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
@@ -3430,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3468,32 +3472,36 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:04</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr"/>
       <c r="K26" s="2" t="inlineStr"/>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -3501,7 +3509,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3525,17 +3533,17 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X26" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y26" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z26" s="2" t="inlineStr">
@@ -3545,17 +3553,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>95.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3583,32 +3591,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:19</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3616,7 +3628,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3640,37 +3652,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3770,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3785,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3813,32 +3825,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3846,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3870,17 +3886,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3890,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3961,7 +3977,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4000,7 +4016,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4072,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4126,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4241,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4302,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4356,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4532,7 +4548,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4647,7 +4663,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4701,7 +4717,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4762,7 +4778,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4816,7 +4832,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4893,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4992,7 +5008,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>09:50</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5036,17 +5052,358 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB39" s="2" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="AC39" s="2" t="inlineStr">
-        <is>
-          <t>10/18</t>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,13 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1962,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2001,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2081,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2120,17 +2124,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2319,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2358,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2438,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2492,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,17 +2957,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3087,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3390,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3563,7 +3567,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3682,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3801,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3916,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3944,32 +3948,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -3977,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4001,17 +4009,17 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
@@ -4021,13 +4029,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB30" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4067,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4088,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,32 +4128,32 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4170,32 +4186,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:55</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -4203,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4247,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4318,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4372,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4433,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4457,32 +4481,32 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4515,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4548,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4572,32 +4600,32 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4630,32 +4658,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:27</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4663,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4687,37 +4719,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4778,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4832,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4893,7 +4925,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4932,7 +4964,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -4975,32 +5007,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:52</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5008,7 +5044,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5032,37 +5068,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5159,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5177,7 +5213,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5274,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5292,7 +5328,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -5300,22 +5336,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5353,7 +5389,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5367,43 +5403,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr"/>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>89.3</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>79.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2967,7 +2967,7 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,17 +4143,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4549,24 +4549,24 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4892,32 +4892,36 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:43</t>
         </is>
       </c>
       <c r="I38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr"/>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N38" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -4925,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4949,17 +4953,17 @@
       </c>
       <c r="W38" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y38" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z38" s="2" t="inlineStr">
@@ -4969,12 +4973,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5017,24 +5021,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11:52</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5044,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5093,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5126,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5159,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5183,37 +5191,37 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5356,32 +5364,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5389,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5413,37 +5425,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5471,32 +5483,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:36</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -5504,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5528,37 +5544,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5586,32 +5602,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5619,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5643,37 +5663,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5701,32 +5721,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5734,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5758,32 +5782,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>91.3</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5849,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5903,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5964,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6013,7 +6037,7 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6079,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6123,12 +6147,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>79.0</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6194,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6243,12 +6267,587 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
           <t>84.7</t>
         </is>
       </c>
-      <c r="AC49" s="2" t="inlineStr">
+      <c r="AC53" s="2" t="inlineStr">
         <is>
           <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>91.3</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,14 +708,14 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,14 +2600,14 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
           <t>86.5</t>
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,17 +2957,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4034,12 +4034,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4153,7 +4153,7 @@
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4968,17 +4968,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5493,24 +5493,24 @@
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>12:36</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5569,12 +5569,12 @@
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5612,12 +5612,12 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5731,12 +5731,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5840,32 +5840,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,37 +5901,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>89.3</t>
+          <t>87.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5955,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5988,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,32 +6020,32 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.7</t>
+          <t>81.5</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6070,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6103,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,32 +6139,32 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>76.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6185,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6218,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,37 +6258,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6387,7 +6403,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6448,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6502,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6612,12 +6628,12 @@
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6727,7 +6743,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6793,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6842,12 +6858,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>91.3</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>87.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>81.5</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>76.3</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,22 +3671,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,17 +4024,17 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,12 +4501,12 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,22 +5206,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6349,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,37 +6377,37 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6431,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,37 +6496,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6546,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -6579,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,32 +6615,32 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6661,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6694,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6718,17 +6734,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6738,12 +6754,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>84.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6776,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6809,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6833,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6853,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6924,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6978,7 +6998,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7039,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7269,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7442,6 +7462,466 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W63" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y63" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z63" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>80.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,17 +946,17 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,12 +1538,12 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,7 +1652,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,17 +2957,17 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,12 +3438,12 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,7 +3552,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,17 +4496,17 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4777,12 +4777,12 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程39%处后消失；随后反向物理轨迹由seq27推进至seq37，推进10站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4818,10 +4818,18 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>五莲路荷泽路</t>
+        </is>
+      </c>
       <c r="R37" s="2" t="inlineStr"/>
       <c r="S37" s="2" t="inlineStr"/>
-      <c r="T37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq17映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4849,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4929,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4973,12 +4981,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5048,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5092,12 +5100,12 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
@@ -5167,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5282,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5401,7 +5409,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5463,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5528,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5582,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5647,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,17 +5686,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5766,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,7 +5805,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5877,7 +5885,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,22 +5924,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5996,7 +6004,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,17 +6043,17 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
@@ -6115,7 +6123,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,12 +6167,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6234,7 +6242,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6278,12 +6286,12 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
@@ -6353,7 +6361,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6472,7 +6480,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6534,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6599,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6645,7 +6653,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6683,24 +6691,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6718,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,17 +6757,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6829,7 +6837,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,7 +6876,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6911,32 +6919,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -6944,7 +6956,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,37 +6980,37 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7026,32 +7038,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7059,7 +7075,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,32 +7099,32 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.5</t>
+          <t>81.6</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
@@ -7141,32 +7157,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:15</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7174,7 +7194,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,17 +7218,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7218,12 +7238,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.3</t>
+          <t>76.0</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7256,32 +7276,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7289,7 +7313,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,17 +7337,17 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
@@ -7333,12 +7357,12 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
@@ -7404,7 +7428,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7458,7 +7482,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7519,7 +7543,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7658,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7712,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7773,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7803,7 +7827,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7864,7 +7888,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7922,6 +7946,1041 @@
         </is>
       </c>
     </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB64" s="2" t="inlineStr">
+        <is>
+          <t>95.5</t>
+        </is>
+      </c>
+      <c r="AC64" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:25</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:40</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>86.4</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>81.6</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC72"/>
+  <dimension ref="A1:AC82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,17 +1414,17 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,7 +3314,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3671,17 +3671,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA27" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,22 +4262,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="Z34" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA34" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5214,17 +5214,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA40" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5257,12 +5257,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq23推进至seq35，推进12站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5298,10 +5298,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5329,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5409,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5448,22 +5460,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5528,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5567,12 +5579,12 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
@@ -5582,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5647,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5686,22 +5698,22 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5820,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5939,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6004,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6058,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6123,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6162,7 +6174,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6242,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6281,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6361,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6400,17 +6412,17 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA50" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6480,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6519,22 +6531,22 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6638,12 +6650,12 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
@@ -6653,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6757,22 +6769,22 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6891,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7010,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7075,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7129,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7194,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:10</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7233,7 +7245,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7286,24 +7298,24 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>15:43</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr">
@@ -7313,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7352,22 +7364,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7395,32 +7407,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -7428,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7452,37 +7468,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>82.3</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7510,32 +7526,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7543,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7567,32 +7587,32 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA60" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
@@ -7625,32 +7645,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7658,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7682,37 +7706,37 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7740,32 +7764,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:14</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -7773,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7797,27 +7825,27 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
@@ -7827,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7855,32 +7883,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:25</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -7888,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7912,37 +7944,37 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>80.0</t>
+          <t>82.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7970,32 +8002,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8003,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8027,32 +8063,32 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>95.5</t>
+          <t>95.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8085,32 +8121,36 @@
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="I65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J65" s="2" t="inlineStr"/>
       <c r="K65" s="2" t="inlineStr"/>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M65" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N65" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8118,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8142,37 +8182,37 @@
       </c>
       <c r="W65" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X65" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y65" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA65" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>82.6</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8233,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8348,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8402,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8463,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8517,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8578,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8693,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8808,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8862,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8923,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8977,7 +9017,1157 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W74" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y74" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z74" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>82.3</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
+        <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>84.4</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>84.0</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>82.5</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>82.6</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>95.3</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC82"/>
+  <dimension ref="A1:AC91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -827,22 +827,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -946,22 +946,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA4" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA4" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1533,22 +1533,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA9" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,17 +1652,17 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,17 +1771,17 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,22 +2719,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2838,22 +2838,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2957,22 +2957,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,22 +3195,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3433,22 +3433,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,17 +3905,17 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4143,7 +4143,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,22 +4857,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5095,22 +5095,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,17 +5341,17 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5817,7 +5817,7 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5936,22 +5936,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6055,22 +6055,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6293,22 +6293,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6888,7 +6888,7 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA54" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7007,22 +7007,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7126,22 +7126,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7364,22 +7364,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -8024,12 +8024,12 @@
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N64" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8240,32 +8240,36 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:38</t>
         </is>
       </c>
       <c r="I66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J66" s="2" t="inlineStr"/>
       <c r="K66" s="2" t="inlineStr"/>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M66" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N66" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8273,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8297,32 +8301,32 @@
       </c>
       <c r="W66" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X66" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y66" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8355,32 +8359,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:44</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -8388,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,37 +8420,37 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA67" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8503,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8542,7 +8550,7 @@
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA68" s="2" t="inlineStr">
@@ -8557,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8585,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8618,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,37 +8654,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8700,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:02</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -8733,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,37 +8773,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>85.5</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8815,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -8848,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,37 +8892,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8930,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8963,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,37 +9011,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA72" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>81.6</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9045,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:30</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -9078,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9102,32 +9130,32 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9193,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:42</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9308,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9332,37 +9364,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA75" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9455,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9477,7 +9509,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9538,7 +9570,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9592,7 +9624,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9653,7 +9685,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9768,7 +9800,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9915,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9937,7 +9969,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10030,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10052,7 +10084,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10113,7 +10145,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10171,6 +10203,1041 @@
         </is>
       </c>
     </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:05</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>85.5</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>83.0</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>17:40</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>17:55</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>99.5</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC91"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,22 +708,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1667,7 +1667,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,17 +2005,17 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,22 +2600,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA18" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3314,17 +3314,17 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3632,7 +3632,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3676,17 +3676,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3796,7 +3796,7 @@
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4024,22 +4024,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4262,17 +4262,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4501,17 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4976,17 +4976,17 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5105,12 +5105,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5175,7 +5175,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5219,17 +5219,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5460,17 +5460,17 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5579,22 +5579,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5703,17 +5703,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6070,7 +6070,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6174,17 +6174,17 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6303,12 +6303,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6417,17 +6417,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6531,17 +6531,17 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6650,22 +6650,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6774,17 +6774,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7245,17 +7245,17 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7374,12 +7374,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,22 +7483,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA59" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7563,7 +7563,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7607,17 +7607,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7721,17 +7721,17 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA61" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7840,22 +7840,22 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7959,22 +7959,22 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9079,24 +9079,24 @@
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>17:30</t>
+          <t>17:31</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>95分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N73" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9155,7 +9155,7 @@
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9188,32 +9188,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:32</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9221,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,32 +9249,32 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>78.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9313,24 +9317,24 @@
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>17:42</t>
+          <t>17:46</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>92分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N75" s="2" t="inlineStr">
@@ -9340,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9389,12 +9393,12 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9422,32 +9426,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:41</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -9455,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9479,37 +9487,37 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA76" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>82.3</t>
+          <t>83.2</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9537,32 +9545,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9570,7 +9582,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9594,17 +9606,17 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
@@ -9614,17 +9626,17 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9652,32 +9664,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>97分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9685,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9709,32 +9725,32 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA78" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>84.4</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
@@ -9767,32 +9783,36 @@
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G79" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:13</t>
         </is>
       </c>
       <c r="I79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J79" s="2" t="inlineStr"/>
       <c r="K79" s="2" t="inlineStr"/>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M79" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N79" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -9800,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9824,37 +9844,37 @@
       </c>
       <c r="W79" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X79" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y79" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>84.0</t>
+          <t>85.8</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9882,32 +9902,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9915,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9939,37 +9963,37 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA80" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>82.5</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9997,32 +10021,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10030,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10054,17 +10082,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10074,17 +10102,17 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>82.6</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10112,32 +10140,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10145,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10169,32 +10201,32 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>95.3</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10260,7 +10292,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10314,7 +10346,7 @@
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10375,7 +10407,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10414,7 +10446,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10429,7 +10461,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10490,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10544,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10605,7 +10637,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10644,7 +10676,7 @@
       </c>
       <c r="Z86" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA86" s="2" t="inlineStr">
@@ -10659,7 +10691,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10720,7 +10752,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10774,7 +10806,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10835,7 +10867,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10889,7 +10921,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10950,7 +10982,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11004,7 +11036,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11065,7 +11097,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11114,12 +11146,12 @@
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11180,7 +11212,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11229,12 +11261,932 @@
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
           <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>78.2</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>85.8</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A52272D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC103"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -708,7 +708,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -723,7 +723,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -832,17 +832,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -951,17 +951,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1066,12 +1066,12 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1494,7 +1494,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1538,17 +1538,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1771,7 +1771,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,22 +2481,22 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2600,7 +2600,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2615,7 +2615,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2799,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2843,17 +2843,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2918,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2962,17 +2962,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3319,12 +3319,12 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3438,17 +3438,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4104,7 +4104,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4148,17 +4148,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="AB34" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4981,12 +4981,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5100,17 +5100,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5341,7 +5341,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5659,7 +5659,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5708,12 +5708,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5822,17 +5822,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5897,7 +5897,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5941,17 +5941,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6016,7 +6016,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6060,17 +6060,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6179,12 +6179,12 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6298,17 +6298,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6730,7 +6730,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6779,12 +6779,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6849,7 +6849,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6893,17 +6893,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7087,7 +7087,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7131,17 +7131,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7325,7 +7325,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7369,17 +7369,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
@@ -7498,7 +7498,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7682,7 +7682,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8207,12 +8207,12 @@
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,22 +8316,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8788,22 +8788,22 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,17 +9031,17 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9145,7 +9145,7 @@
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9269,12 +9269,12 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9344,7 +9344,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9388,17 +9388,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9502,7 +9502,7 @@
       </c>
       <c r="Z76" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA76" s="2" t="inlineStr">
@@ -9517,7 +9517,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9701,7 +9701,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -10031,24 +10031,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>108分钟</t>
+          <t>107分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10107,12 +10107,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10259,32 +10259,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:33</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10292,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10316,37 +10320,37 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10374,32 +10378,36 @@
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:42</t>
         </is>
       </c>
       <c r="I84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J84" s="2" t="inlineStr"/>
       <c r="K84" s="2" t="inlineStr"/>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M84" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N84" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -10407,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10431,17 +10439,17 @@
       </c>
       <c r="W84" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X84" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y84" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z84" s="2" t="inlineStr">
@@ -10451,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10489,32 +10497,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10522,7 +10534,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10546,17 +10558,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10566,17 +10578,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -10604,32 +10616,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10637,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10661,17 +10677,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10681,17 +10697,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10719,32 +10735,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -10752,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10776,37 +10796,37 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>85.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10834,32 +10854,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10867,7 +10891,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10891,17 +10915,17 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
@@ -10911,17 +10935,17 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>83.0</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10949,32 +10973,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:18</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -10982,7 +11010,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11006,17 +11034,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11026,17 +11054,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11064,32 +11092,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11097,7 +11129,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11121,17 +11153,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11141,17 +11173,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11212,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11251,7 +11283,7 @@
       </c>
       <c r="Z91" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA91" s="2" t="inlineStr">
@@ -11327,7 +11359,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11381,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11409,32 +11441,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -11442,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11466,17 +11502,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11486,12 +11522,12 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>78.2</t>
+          <t>78.5</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11557,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11596,7 +11632,7 @@
       </c>
       <c r="Z94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA94" s="2" t="inlineStr">
@@ -11611,7 +11647,7 @@
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -11672,7 +11708,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11787,7 +11823,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11841,7 +11877,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11902,7 +11938,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11946,17 +11982,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12017,7 +12053,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12132,7 +12168,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12176,17 +12212,477 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>90.7</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A58633D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AB99" s="2" t="inlineStr">
-        <is>
-          <t>88.0</t>
-        </is>
-      </c>
-      <c r="AC99" s="2" t="inlineStr">
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
         <is>
           <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr"/>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E103" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G103" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J103" s="2" t="inlineStr"/>
+      <c r="K103" s="2" t="inlineStr"/>
+      <c r="L103" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr"/>
+      <c r="N103" s="2" t="inlineStr">
+        <is>
+          <t>06:00</t>
+        </is>
+      </c>
+      <c r="O103" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P103" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q103" s="2" t="inlineStr"/>
+      <c r="R103" s="2" t="inlineStr"/>
+      <c r="S103" s="2" t="inlineStr"/>
+      <c r="T103" s="2" t="inlineStr"/>
+      <c r="U103" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W103" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X103" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y103" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z103" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA103" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB103" s="2" t="inlineStr">
+        <is>
+          <t>83.2</t>
+        </is>
+      </c>
+      <c r="AC103" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AC106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1071,7 +1071,7 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,17 +1295,17 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1652,22 +1652,22 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,12 +1891,12 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,17 +2248,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2680,7 +2680,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3200,17 +3200,17 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3275,7 +3275,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3552,17 +3552,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA26" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA29" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3985,7 +3985,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4029,12 +4029,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4862,17 +4862,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4986,7 +4986,7 @@
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5584,12 +5584,12 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6135,7 +6135,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6611,7 +6611,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7206,7 +7206,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7801,7 +7801,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
@@ -7920,7 +7920,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7964,17 +7964,17 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8078,17 +8078,17 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8316,22 +8316,22 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA66" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8396,7 +8396,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8440,17 +8440,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,17 +8674,17 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9274,7 +9274,7 @@
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9820,7 +9820,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
@@ -9939,7 +9939,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9983,17 +9983,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10216,17 +10216,17 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA82" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10335,22 +10335,22 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA83" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10415,7 +10415,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10459,17 +10459,17 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10697,17 +10697,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="Z87" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA87" s="2" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11451,24 +11451,24 @@
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>19:30</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N93" s="2" t="inlineStr">
@@ -11478,7 +11478,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11527,7 +11527,7 @@
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>78.5</t>
+          <t>78.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11675,32 +11675,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:56</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11708,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11732,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11752,17 +11756,17 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11790,32 +11794,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:02</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11823,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:00</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11847,17 +11855,17 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
@@ -11867,12 +11875,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>85.8</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11905,32 +11913,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>07:00</t>
@@ -11938,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11962,17 +11974,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11982,17 +11994,17 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12020,32 +12032,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:25</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12053,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12077,32 +12093,32 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA98" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12135,32 +12151,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>75分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -12168,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12192,17 +12212,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12212,17 +12232,17 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12250,32 +12270,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:48</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12283,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12307,37 +12331,37 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA100" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12398,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12513,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12552,7 +12576,7 @@
       </c>
       <c r="Z102" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA102" s="2" t="inlineStr">
@@ -12567,7 +12591,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12628,7 +12652,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12686,6 +12710,351 @@
         </is>
       </c>
     </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr"/>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E104" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G104" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J104" s="2" t="inlineStr"/>
+      <c r="K104" s="2" t="inlineStr"/>
+      <c r="L104" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr"/>
+      <c r="N104" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O104" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P104" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q104" s="2" t="inlineStr"/>
+      <c r="R104" s="2" t="inlineStr"/>
+      <c r="S104" s="2" t="inlineStr"/>
+      <c r="T104" s="2" t="inlineStr"/>
+      <c r="U104" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W104" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X104" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y104" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z104" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA104" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB104" s="2" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="AC104" s="2" t="inlineStr">
+        <is>
+          <t>17/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr"/>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J105" s="2" t="inlineStr"/>
+      <c r="K105" s="2" t="inlineStr"/>
+      <c r="L105" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr"/>
+      <c r="N105" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O105" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P105" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q105" s="2" t="inlineStr"/>
+      <c r="R105" s="2" t="inlineStr"/>
+      <c r="S105" s="2" t="inlineStr"/>
+      <c r="T105" s="2" t="inlineStr"/>
+      <c r="U105" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W105" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X105" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y105" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z105" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA105" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB105" s="2" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="AC105" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr"/>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J106" s="2" t="inlineStr"/>
+      <c r="K106" s="2" t="inlineStr"/>
+      <c r="L106" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M106" s="2" t="inlineStr"/>
+      <c r="N106" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="O106" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P106" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q106" s="2" t="inlineStr"/>
+      <c r="R106" s="2" t="inlineStr"/>
+      <c r="S106" s="2" t="inlineStr"/>
+      <c r="T106" s="2" t="inlineStr"/>
+      <c r="U106" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W106" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X106" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y106" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z106" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA106" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB106" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC106" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -669,7 +669,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -713,12 +713,12 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -842,7 +842,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,17 +1300,17 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1548,7 +1548,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1662,12 +1662,12 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1732,7 +1732,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB17" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2605,12 +2605,12 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2853,7 +2853,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3091,7 +3091,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3156,7 +3156,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3210,7 +3210,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3557,17 +3557,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4872,7 +4872,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5110,7 +5110,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5229,7 +5229,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5346,12 +5346,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5832,7 +5832,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6308,7 +6308,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6427,7 +6427,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6784,7 +6784,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6903,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7379,7 +7379,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7444,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7488,12 +7488,12 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7974,7 @@
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8083,17 +8083,17 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,12 +9150,12 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
@@ -9398,7 +9398,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9463,7 +9463,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9993,7 +9993,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -10112,7 +10112,7 @@
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10221,17 +10221,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10345,12 +10345,12 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10588,7 +10588,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10653,7 +10653,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10707,7 +10707,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10816,17 +10816,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11064,7 +11064,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -11183,7 +11183,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11244,7 +11244,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11288,12 +11288,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11593,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11637,12 +11637,12 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
@@ -11766,7 +11766,7 @@
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12113,17 +12113,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12242,7 +12242,7 @@
       </c>
       <c r="AC99" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -12280,24 +12280,24 @@
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>20:48</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>78分钟</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N100" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12356,12 +12356,12 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12389,32 +12389,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:07</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12422,7 +12426,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12446,17 +12450,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12466,12 +12470,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>92.3</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12504,32 +12508,36 @@
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G102" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:15</t>
         </is>
       </c>
       <c r="I102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J102" s="2" t="inlineStr"/>
       <c r="K102" s="2" t="inlineStr"/>
       <c r="L102" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M102" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N102" s="2" t="inlineStr">
         <is>
           <t>06:40</t>
@@ -12537,7 +12545,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12561,17 +12569,17 @@
       </c>
       <c r="W102" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X102" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y102" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z102" s="2" t="inlineStr">
@@ -12581,17 +12589,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12619,32 +12627,36 @@
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G103" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:25</t>
         </is>
       </c>
       <c r="I103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>70分钟</t>
         </is>
       </c>
       <c r="J103" s="2" t="inlineStr"/>
       <c r="K103" s="2" t="inlineStr"/>
       <c r="L103" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M103" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M103" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N103" s="2" t="inlineStr">
         <is>
           <t>06:00</t>
@@ -12652,7 +12664,7 @@
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P103" s="2" t="inlineStr">
@@ -12676,17 +12688,17 @@
       </c>
       <c r="W103" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X103" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y103" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z103" s="2" t="inlineStr">
@@ -12696,12 +12708,12 @@
       </c>
       <c r="AA103" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB103" s="2" t="inlineStr">
         <is>
-          <t>83.2</t>
+          <t>80.6</t>
         </is>
       </c>
       <c r="AC103" s="2" t="inlineStr">
@@ -12734,32 +12746,36 @@
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G104" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:57</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>77分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
       <c r="K104" s="2" t="inlineStr"/>
       <c r="L104" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M104" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M104" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N104" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12767,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12791,17 +12807,17 @@
       </c>
       <c r="W104" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X104" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y104" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z104" s="2" t="inlineStr">
@@ -12811,17 +12827,17 @@
       </c>
       <c r="AA104" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12882,7 +12898,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12931,12 +12947,12 @@
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -12997,7 +13013,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13041,17 +13057,17 @@
       </c>
       <c r="AA106" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB106" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-09-29-浦东78路.xlsx
+++ b/data/export/2026-09-29-浦东78路.xlsx
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1305,7 +1305,7 @@
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1657,17 +1657,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2442,7 +2442,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2734,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3513,7 +3513,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3866,7 +3866,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3910,17 +3910,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4039,7 +4039,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4277,7 +4277,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5475,7 +5475,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5594,7 +5594,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6665,7 +6665,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7736,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7855,7 +7855,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -8039,7 +8039,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8088,7 +8088,7 @@
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8277,7 +8277,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8321,17 +8321,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9874,7 +9874,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10177,7 +10177,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10226,7 +10226,7 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10296,7 +10296,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10340,17 +10340,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10772,7 +10772,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10826,7 +10826,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -11413,7 +11413,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -11885,7 +11885,7 @@
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -12004,7 +12004,7 @@
       </c>
       <c r="AC97" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12118,7 +12118,7 @@
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12351,17 +12351,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -12545,7 +12545,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12599,7 +12599,7 @@
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -12756,12 +12756,12 @@
       </c>
       <c r="H104" s="2" t="inlineStr">
         <is>
-          <t>21:57</t>
+          <t>21:58</t>
         </is>
       </c>
       <c r="I104" s="2" t="inlineStr">
         <is>
-          <t>77分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J104" s="2" t="inlineStr"/>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P104" s="2" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="AB104" s="2" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>89.3</t>
         </is>
       </c>
       <c r="AC104" s="2" t="inlineStr">
@@ -12865,32 +12865,36 @@
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G105" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:26</t>
         </is>
       </c>
       <c r="I105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J105" s="2" t="inlineStr"/>
       <c r="K105" s="2" t="inlineStr"/>
       <c r="L105" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M105" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M105" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N105" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12898,7 +12902,7 @@
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P105" s="2" t="inlineStr">
@@ -12922,17 +12926,17 @@
       </c>
       <c r="W105" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X105" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y105" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z105" s="2" t="inlineStr">
@@ -12942,17 +12946,17 @@
       </c>
       <c r="AA105" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB105" s="2" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="AC105" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13017,7 @@
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P106" s="2" t="inlineStr">
@@ -13067,7 +13071,7 @@
       </c>
       <c r="AC106" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
